--- a/data/excel/Administration_AvenueManagement_CancellationCharges.xlsx
+++ b/data/excel/Administration_AvenueManagement_CancellationCharges.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A846B71-FE2B-4DAF-B3EF-A046A3D23135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC15DA1-4523-4505-8071-F441A47539CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3390" yWindow="3510" windowWidth="25410" windowHeight="6570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="73">
   <si>
     <t>TestCaseId</t>
   </si>
@@ -55,15 +56,6 @@
     <t>qlabs12345</t>
   </si>
   <si>
-    <t>Verify Corporate Profiling</t>
-  </si>
-  <si>
-    <t>Piyush_QL</t>
-  </si>
-  <si>
-    <t>Password@123456</t>
-  </si>
-  <si>
     <t>RuleTemplateTitle</t>
   </si>
   <si>
@@ -97,9 +89,6 @@
     <t>Airlines</t>
   </si>
   <si>
-    <t>Air India [AI],IndiGo [6E],Gulf Air [GF]</t>
-  </si>
-  <si>
     <t>CabinQty</t>
   </si>
   <si>
@@ -220,12 +209,6 @@
     <t>BookDateTo</t>
   </si>
   <si>
-    <t>11-Jan-2025</t>
-  </si>
-  <si>
-    <t>11-Feb-2025</t>
-  </si>
-  <si>
     <t>FareTQty</t>
   </si>
   <si>
@@ -236,6 +219,27 @@
   </si>
   <si>
     <t>Airline,Cabin Class,Origin,Destination,Booking Class,Pax Type,Base Fare,Booking Date,Fare Type,Group,B2B/Corporate</t>
+  </si>
+  <si>
+    <t>Piyush_ql</t>
+  </si>
+  <si>
+    <t>EE6B4B@E7</t>
+  </si>
+  <si>
+    <t>11-May-2025</t>
+  </si>
+  <si>
+    <t>30-May-2025</t>
+  </si>
+  <si>
+    <t>Air India Limited [AI],IndiGo [6E],Gulf Air [GF]</t>
+  </si>
+  <si>
+    <t>Verify Cancellation Charges Rule</t>
+  </si>
+  <si>
+    <t>Test124</t>
   </si>
 </sst>
 </file>
@@ -324,21 +328,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -629,11 +656,11 @@
     <col min="4" max="4" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="76" style="8" customWidth="1"/>
+    <col min="11" max="11" width="76" style="2" customWidth="1"/>
     <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="108.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="34.7109375" bestFit="1" customWidth="1"/>
@@ -670,314 +697,305 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="P1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="Q1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="O1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P1" s="6" t="s">
+      <c r="R1" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y1" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA1" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="R1" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y1" s="2" t="s">
+      <c r="AF1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK1" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="AL1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AN1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AO1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AA1" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AP1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="AC1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE1" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="AF1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AH1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AI1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AJ1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AL1" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AM1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AO1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AR1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AS1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AT1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AU1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AV1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AW1" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="AT1" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="AU1" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AV1" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="AW1" s="6" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:49" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2">
-        <v>6</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2">
-        <v>9</v>
-      </c>
-      <c r="M2" t="s">
-        <v>71</v>
-      </c>
-      <c r="N2">
-        <v>3</v>
-      </c>
-      <c r="O2" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2">
-        <v>3</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>28</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="S2">
-        <v>1</v>
-      </c>
-      <c r="T2" s="3" t="s">
+      <c r="F2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="N2" s="2">
+        <v>1</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P2" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="S2" s="2">
+        <v>1</v>
+      </c>
+      <c r="T2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="U2" s="2">
+        <v>1</v>
+      </c>
+      <c r="V2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="W2" s="2">
+        <v>1</v>
+      </c>
+      <c r="X2" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="U2">
-        <v>1</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="W2">
-        <v>1</v>
-      </c>
-      <c r="X2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y2">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA2">
-        <v>1</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD2">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="3" t="s">
+      <c r="AC2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD2" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF2" s="2">
+        <v>2</v>
+      </c>
+      <c r="AG2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH2" s="2">
+        <v>2</v>
+      </c>
+      <c r="AI2" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ2" s="2">
+        <v>1</v>
+      </c>
+      <c r="AK2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL2" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM2" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AF2">
-        <v>2</v>
-      </c>
-      <c r="AG2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH2">
-        <v>2</v>
-      </c>
-      <c r="AI2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AJ2">
-        <v>1</v>
-      </c>
-      <c r="AK2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="AL2">
-        <v>1</v>
-      </c>
-      <c r="AM2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AN2">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AP2">
-        <v>1</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AR2">
+      <c r="AN2" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP2" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AR2" s="2">
         <v>2000</v>
       </c>
-      <c r="AS2">
+      <c r="AS2" s="2">
         <v>20000</v>
       </c>
       <c r="AT2" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AU2" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="AV2">
-        <v>1</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="AV2" s="2">
+        <v>1</v>
+      </c>
+      <c r="AW2" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>"at,qlabs12345"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{00000000-0002-0000-0000-000003000000}">
-      <formula1>"Piyush_QL"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{00000000-0002-0000-0000-000004000000}">
-      <formula1>"Password@123456"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{166FA201-9B98-4A76-8C71-F3A61F7A0264}">
       <formula1>"Flight,Bus,Car,Hotel,Insurance,Meet and Greet Service,Sightseeing,Transfer"</formula1>
     </dataValidation>
@@ -990,12 +1008,354 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2" xr:uid="{CFFBCD7F-DC98-4F18-9E41-62CF0B150EF0}">
       <formula1>"1,2,3,4,5,6,7,8,9"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{BF36970E-9F53-4202-A3DF-3B28B3502A38}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{39BB2BAC-5BF1-4E17-872A-733C7C43334F}">
+      <formula1>"at,qlabs12345,merg123456"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{DD82AEE0-2E4E-4C38-894C-30EADE05320B}">
+      <formula1>"EE6B4B@E7,07DE6@EAB,F1CD@9E4B"</formula1>
+    </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="shubham.natkar@quadlabs.com" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="G2" r:id="rId2" display="Piyush@321" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{74D88371-A544-4892-9277-AB0529474B0D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0E9ED37-536F-4E3D-B90A-C89D527B80DF}">
+  <dimension ref="A1:AW2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q1" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="T1" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="U1" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="V1" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="W1" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="X1" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y1" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z1" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA1" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB1" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC1" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD1" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE1" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF1" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG1" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH1" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI1" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ1" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK1" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="AL1" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM1" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="AN1" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="AO1" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP1" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="AQ1" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="AR1" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="AS1" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="AT1" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="AU1" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AV1" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="AW1" s="12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="15">
+        <v>2</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="15">
+        <v>8</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="N2" s="15">
+        <v>1</v>
+      </c>
+      <c r="O2" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="P2" s="15">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="S2" s="15">
+        <v>1</v>
+      </c>
+      <c r="T2" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="U2" s="15">
+        <v>1</v>
+      </c>
+      <c r="V2" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="W2" s="15">
+        <v>1</v>
+      </c>
+      <c r="X2" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y2" s="15">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA2" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC2" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD2" s="15">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF2" s="15">
+        <v>2</v>
+      </c>
+      <c r="AG2" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH2" s="15">
+        <v>2</v>
+      </c>
+      <c r="AI2" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ2" s="15">
+        <v>1</v>
+      </c>
+      <c r="AK2" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL2" s="15">
+        <v>1</v>
+      </c>
+      <c r="AM2" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN2" s="15">
+        <v>1</v>
+      </c>
+      <c r="AO2" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP2" s="15">
+        <v>1</v>
+      </c>
+      <c r="AQ2" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="AR2" s="15">
+        <v>2000</v>
+      </c>
+      <c r="AS2" s="15">
+        <v>20000</v>
+      </c>
+      <c r="AT2" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU2" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="AV2" s="15">
+        <v>1</v>
+      </c>
+      <c r="AW2" s="15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{296B0777-4100-4722-8FBF-6C1DFD1F43CA}">
+      <formula1>"EE6B4B@E7,07DE6@EAB,F1CD@9E4B"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{984E2540-74E3-4F04-9A7D-C49F5828FEE8}">
+      <formula1>"at,qlabs12345,merg123456"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{FF8A51F2-8645-4AA2-8055-CE6BE832129B}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2" xr:uid="{391C2500-A06B-4ABA-BD14-9CA7098F0D97}">
+      <formula1>"1,2,3,4,5,6,7,8,9"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 AC2" xr:uid="{EEFD6A78-AEE4-467A-8CA5-F42FD0DC3FDC}">
+      <formula1>"Zone,Region,Country,City,Airport"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2 AV2 N2 P2 AD2 AL2 AJ2 AH2 AF2 AP2 AA2 Y2 W2 U2 S2 AN2" xr:uid="{81B1BAA6-4F48-46A6-9A7A-EDF422F84521}">
+      <formula1>"1,2,3,4,5,6,7"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{A806B55F-BA6F-45EF-87E9-A32BE99C5310}">
+      <formula1>"Flight,Bus,Car,Hotel,Insurance,Meet and Greet Service,Sightseeing,Transfer"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{5BB85976-183F-4672-90D1-176FBE424FD8}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/excel/Administration_AvenueManagement_CancellationCharges.xlsx
+++ b/data/excel/Administration_AvenueManagement_CancellationCharges.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC15DA1-4523-4505-8071-F441A47539CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A98112-B359-44B3-B64E-7AC2AA7CEA82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="76">
   <si>
     <t>TestCaseId</t>
   </si>
@@ -239,7 +239,16 @@
     <t>Verify Cancellation Charges Rule</t>
   </si>
   <si>
-    <t>Test124</t>
+    <t>k.gaurav</t>
+  </si>
+  <si>
+    <t>07DE6@EAB</t>
+  </si>
+  <si>
+    <t>Test MO 2</t>
+  </si>
+  <si>
+    <t>Test127</t>
   </si>
 </sst>
 </file>
@@ -328,7 +337,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -357,15 +366,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1182,7 +1187,7 @@
     </row>
     <row r="2" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>71</v>
@@ -1196,70 +1201,70 @@
       <c r="E2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="14" t="s">
-        <v>66</v>
+      <c r="F2" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="I2" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="15">
+      <c r="J2">
         <v>2</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="15">
+      <c r="L2">
         <v>8</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" t="s">
         <v>65</v>
       </c>
-      <c r="N2" s="15">
-        <v>1</v>
-      </c>
-      <c r="O2" s="15" t="s">
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2" t="s">
         <v>70</v>
       </c>
-      <c r="P2" s="15">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="15" t="s">
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="s">
         <v>24</v>
       </c>
       <c r="R2" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="S2" s="15">
+      <c r="S2">
         <v>1</v>
       </c>
       <c r="T2" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="U2" s="15">
+      <c r="U2">
         <v>1</v>
       </c>
       <c r="V2" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="W2" s="15">
+      <c r="W2">
         <v>1</v>
       </c>
       <c r="X2" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="Y2" s="15">
+      <c r="Y2">
         <v>1</v>
       </c>
       <c r="Z2" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="AA2" s="15">
+      <c r="AA2">
         <v>1</v>
       </c>
       <c r="AB2" s="13" t="s">
@@ -1268,76 +1273,76 @@
       <c r="AC2" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AD2" s="15">
+      <c r="AD2">
         <v>1</v>
       </c>
       <c r="AE2" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="AF2" s="15">
+      <c r="AF2">
         <v>2</v>
       </c>
       <c r="AG2" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AH2" s="15">
+      <c r="AH2">
         <v>2</v>
       </c>
       <c r="AI2" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="AJ2" s="15">
+      <c r="AJ2">
         <v>1</v>
       </c>
       <c r="AK2" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="AL2" s="15">
+      <c r="AL2">
         <v>1</v>
       </c>
       <c r="AM2" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="AN2" s="15">
-        <v>1</v>
-      </c>
-      <c r="AO2" s="15" t="s">
+      <c r="AN2">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="s">
         <v>54</v>
       </c>
-      <c r="AP2" s="15">
-        <v>1</v>
-      </c>
-      <c r="AQ2" s="15" t="s">
+      <c r="AP2">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="s">
         <v>57</v>
       </c>
-      <c r="AR2" s="15">
+      <c r="AR2">
         <v>2000</v>
       </c>
-      <c r="AS2" s="15">
+      <c r="AS2">
         <v>20000</v>
       </c>
-      <c r="AT2" s="16" t="s">
+      <c r="AT2" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="AU2" s="16" t="s">
+      <c r="AU2" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="AV2" s="15">
-        <v>1</v>
-      </c>
-      <c r="AW2" s="15" t="s">
+      <c r="AV2">
+        <v>1</v>
+      </c>
+      <c r="AW2" t="s">
         <v>64</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{296B0777-4100-4722-8FBF-6C1DFD1F43CA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{8EF66D61-897C-4CB1-B740-A1693F81FBCE}">
       <formula1>"EE6B4B@E7,07DE6@EAB,F1CD@9E4B"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{984E2540-74E3-4F04-9A7D-C49F5828FEE8}">
       <formula1>"at,qlabs12345,merg123456"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{FF8A51F2-8645-4AA2-8055-CE6BE832129B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{A32342E6-29D6-49FD-9813-D6ECBE5B3627}">
       <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2" xr:uid="{391C2500-A06B-4ABA-BD14-9CA7098F0D97}">
@@ -1354,7 +1359,7 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{5BB85976-183F-4672-90D1-176FBE424FD8}"/>
+    <hyperlink ref="G2" r:id="rId1" display="EE6B4B@E7" xr:uid="{79D0FEE5-D1E4-4144-9E6A-9FFB710E9FCC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
